--- a/Tagihan/2026/Agustus/Denso.xlsx
+++ b/Tagihan/2026/Agustus/Denso.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Agustus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{479DFC20-3298-4953-A7C2-975A1B6E751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA86BFB-FFA3-4E88-8014-FBC9401200C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perbaikan" sheetId="1" r:id="rId1"/>
@@ -208,7 +208,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -561,38 +561,38 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -643,7 +643,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -664,11 +664,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
